--- a/docs/evidencia/informe/ejemplo-excel.xlsx
+++ b/docs/evidencia/informe/ejemplo-excel.xlsx
@@ -6,13 +6,16 @@
   <sheets>
     <sheet sheetId="1" name="Resumen" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Compras" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Asignaciones" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Fondos y saldos" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Comprobantes" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="78">
   <si>
     <t>Informe</t>
   </si>
@@ -20,6 +23,12 @@
     <t>Rendición de gastos</t>
   </si>
   <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Rendición de gastos por gestión</t>
+  </si>
+  <si>
     <t>Identificador</t>
   </si>
   <si>
@@ -35,6 +44,18 @@
     <t>Winston Managua</t>
   </si>
   <si>
+    <t>Apertura y cierre</t>
+  </si>
+  <si>
+    <t>20/10/2026 — abierta</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Compras de la jornada en Managua</t>
+  </si>
+  <si>
     <t>Responsable</t>
   </si>
   <si>
@@ -47,31 +68,22 @@
     <t>Empresa de ejemplo S.A.</t>
   </si>
   <si>
-    <t>Apertura</t>
-  </si>
-  <si>
-    <t>20/10/2026</t>
-  </si>
-  <si>
-    <t>Cierre</t>
+    <t>Corte</t>
   </si>
   <si>
     <t>27/10/2026</t>
   </si>
   <si>
-    <t>Corte</t>
-  </si>
-  <si>
     <t>Emitido (UTC)</t>
   </si>
   <si>
-    <t>2026-10-27T21:30:00.000Z</t>
-  </si>
-  <si>
-    <t>Liquidación</t>
-  </si>
-  <si>
-    <t>No calculada en esta versión</t>
+    <t>2026-10-27T21:50:00.000Z</t>
+  </si>
+  <si>
+    <t>Liquidación: Winston Managua</t>
+  </si>
+  <si>
+    <t>parcial</t>
   </si>
   <si>
     <t>Moneda</t>
@@ -104,103 +116,139 @@
     <t>Concepto</t>
   </si>
   <si>
+    <t>Importe de la compra</t>
+  </si>
+  <si>
+    <t>Importe en este informe</t>
+  </si>
+  <si>
+    <t>Soporte</t>
+  </si>
+  <si>
+    <t>Identificador interno</t>
+  </si>
+  <si>
+    <t>21/10/2026</t>
+  </si>
+  <si>
+    <t>Supermercado Ejemplo S.A.</t>
+  </si>
+  <si>
+    <t>0000123</t>
+  </si>
+  <si>
+    <t>Compra supermercado</t>
+  </si>
+  <si>
+    <t>A-01</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>22/10/2026</t>
+  </si>
+  <si>
+    <t>Ferretería Demostración</t>
+  </si>
+  <si>
+    <t>0000124</t>
+  </si>
+  <si>
+    <t>Materiales de la jornada</t>
+  </si>
+  <si>
+    <t>A-02, A-03</t>
+  </si>
+  <si>
+    <t>c2</t>
+  </si>
+  <si>
+    <t>23/10/2026</t>
+  </si>
+  <si>
+    <t>Restaurante Muestra</t>
+  </si>
+  <si>
+    <t>0000125</t>
+  </si>
+  <si>
+    <t>Alimentación</t>
+  </si>
+  <si>
+    <t>A-04</t>
+  </si>
+  <si>
+    <t>c3</t>
+  </si>
+  <si>
+    <t>24/10/2026</t>
+  </si>
+  <si>
+    <t>Peaje Carretera Norte</t>
+  </si>
+  <si>
+    <t>Sin número</t>
+  </si>
+  <si>
+    <t>Peaje</t>
+  </si>
+  <si>
+    <t>Pendiente</t>
+  </si>
+  <si>
+    <t>c4</t>
+  </si>
+  <si>
+    <t>25/10/2026</t>
+  </si>
+  <si>
+    <t>Taller Ejemplo</t>
+  </si>
+  <si>
+    <t>0004410</t>
+  </si>
+  <si>
+    <t>Repuesto a crédito</t>
+  </si>
+  <si>
+    <t>A-05</t>
+  </si>
+  <si>
+    <t>c5</t>
+  </si>
+  <si>
+    <t>Compra N.°</t>
+  </si>
+  <si>
+    <t>Destino</t>
+  </si>
+  <si>
     <t>Importe</t>
   </si>
   <si>
-    <t>Soporte</t>
-  </si>
-  <si>
-    <t>Identificador interno</t>
-  </si>
-  <si>
-    <t>21/10/2026</t>
-  </si>
-  <si>
-    <t>Supermercado Ejemplo S.A.</t>
-  </si>
-  <si>
-    <t>0000123</t>
-  </si>
-  <si>
-    <t>Compra supermercado</t>
-  </si>
-  <si>
-    <t>A-01</t>
-  </si>
-  <si>
-    <t>c1</t>
-  </si>
-  <si>
-    <t>22/10/2026</t>
-  </si>
-  <si>
-    <t>Ferretería Demostración</t>
-  </si>
-  <si>
-    <t>0000124</t>
-  </si>
-  <si>
-    <t>Combustible y materiales de la jornada</t>
-  </si>
-  <si>
-    <t>A-02, A-03</t>
-  </si>
-  <si>
-    <t>c2</t>
-  </si>
-  <si>
-    <t>23/10/2026</t>
-  </si>
-  <si>
-    <t>Restaurante Muestra</t>
-  </si>
-  <si>
-    <t>0000125</t>
-  </si>
-  <si>
-    <t>Alimentación</t>
-  </si>
-  <si>
-    <t>A-04</t>
-  </si>
-  <si>
-    <t>c3</t>
-  </si>
-  <si>
-    <t>24/10/2026</t>
-  </si>
-  <si>
-    <t>Peaje Carretera Norte</t>
-  </si>
-  <si>
-    <t>Sin número</t>
-  </si>
-  <si>
-    <t>Peaje</t>
-  </si>
-  <si>
-    <t>Pendiente</t>
-  </si>
-  <si>
-    <t>c4</t>
-  </si>
-  <si>
-    <t>25/10/2026</t>
-  </si>
-  <si>
-    <t>Taller Ejemplo</t>
-  </si>
-  <si>
-    <t>0004410</t>
-  </si>
-  <si>
-    <t>Reparación de llanta</t>
-  </si>
-  <si>
-    <t>Ausente: falta la imagen</t>
-  </si>
-  <si>
-    <t>c5</t>
+    <t>Persona de ejemplo</t>
+  </si>
+  <si>
+    <t>Pendiente de pago a Taller Ejemplo, deudor Empresa de ejemplo S.A.</t>
+  </si>
+  <si>
+    <t>Por reembolsar al responsable, a cargo de Empresa de ejemplo S.A.</t>
+  </si>
+  <si>
+    <t>Por reembolsar al responsable, a cargo de Persona de ejemplo</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Anexos</t>
+  </si>
+  <si>
+    <t>Imágenes</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -589,11 +637,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -617,16 +665,16 @@
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>1</v>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
         <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -666,55 +714,63 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="1" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="B12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="14" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="2">
-        <v>13200.75</v>
-      </c>
-      <c r="C14">
-        <v>4</v>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="3">
+        <v>26</v>
+      </c>
+      <c r="B15" s="2">
+        <v>19050.75</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="3">
         <v>85</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>1</v>
       </c>
     </row>
@@ -726,192 +782,491 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="36" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="38" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="36" customWidth="1"/>
+    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>36</v>
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="5">
+        <v>40</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="5">
         <v>8200</v>
       </c>
-      <c r="H2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I2" s="5">
+        <v>8200</v>
+      </c>
+      <c r="J2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" t="s">
-        <v>42</v>
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="5">
+        <v>46</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="5">
         <v>4250.75</v>
       </c>
-      <c r="H3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I3" s="5">
+        <v>4250.75</v>
+      </c>
+      <c r="J3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" t="s">
-        <v>48</v>
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="5">
+        <v>52</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="5">
         <v>85</v>
       </c>
-      <c r="H4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I4" s="5">
+        <v>85</v>
+      </c>
+      <c r="J4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" t="s">
-        <v>54</v>
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="5">
+        <v>58</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="5">
         <v>100</v>
       </c>
-      <c r="H5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I5" s="5">
+        <v>100</v>
+      </c>
+      <c r="J5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="5">
+        <v>6500</v>
+      </c>
+      <c r="I6" s="5">
+        <v>6500</v>
+      </c>
+      <c r="J6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="5">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="5">
+        <v>3250.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="5">
+        <v>6500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="5">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1450.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="5">
+        <v>400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>59</v>
       </c>
-      <c r="E6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="5">
-        <v>650</v>
-      </c>
-      <c r="H6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I6" t="s">
-        <v>62</v>
+      <c r="C5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
